--- a/Result/checksun_type/專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等).xlsx
+++ b/Result/checksun_type/專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>12.62</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>12.68</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>12.82</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12.82</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>300.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>838.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>838.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>561.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>466.84</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>466.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>126.6976446948441</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>300</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>12.64</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>12.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3110.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>861.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>861.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>560.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>479.34</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>479.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>194.028947364287</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3110</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3110.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>12.68</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>295.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>334.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>334.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>320.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>429.26</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>429.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-17.78451122809048</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>295</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>295.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>12.69</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>409.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>321.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>321</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>312.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>431.96</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>431.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-18.13286238762663</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>409</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>409.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>12.68</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>12.82</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>12.92</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12.92</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>80.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>281.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>281</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>334.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>433.14</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>433.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-30.19719038740584</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>80</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>12.62</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>12.94</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.94</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>414.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>283.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>283.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>349.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>440.86</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>440.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-11.10347358754024</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>414</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>414.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>12.56</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>12.97</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12.97</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>474.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>260.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>260.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>360.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>448.92</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>448.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-19.2158969596058</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>474</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>474.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>12.52</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>12.99</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>228.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>306.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>306.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>344.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>454.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>454</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-36.54736259971355</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>228</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>12.49</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>209.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>303.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>303.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>339.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>461.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>461.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-33.64419342130628</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>209</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>209.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>12.48</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>12.91</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>13.01</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>92.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>387.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>387</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>347.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>462.22</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>462.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-26.25951625853503</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>92</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>12.56</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>12.94</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>13.02</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>298.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>414.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>414.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>391.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>472.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>472.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2.236423302485491</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>298</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>14.36</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15.49</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>927.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>600</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>952.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1433.74</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1433.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-143.4216210361842</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>927</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>927.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>14.47</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15.53</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>242.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>614.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>614.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>948.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1453.92</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1453.92</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-172.6395609249306</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>242</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>14.45</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15.57</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>513.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1104.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1104.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1065.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1462.6</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1462.6</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-134.8209193043924</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>513</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>513.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>14.7</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1168.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1109.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1109.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1121.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1481.88</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1481.88</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-105.0149698713237</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1168</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1168.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>150.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1000.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1000.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1068.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1530.2</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1530.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-128.863078900107</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>150</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>15.21</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>15.68</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>15.68</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>15.68</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1000.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1305.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1305.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1159.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1532.32</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1532.32</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-49.25812469479342</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1000</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>15.39</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>15.75</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15.7</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2690.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1281.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1281.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1182.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1523.64</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1523.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-24.8489713766744</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2690</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2690.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>15.67</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>15.84</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>15.73</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15.73</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>541.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1026.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1026</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1012.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1475.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1475.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-170.1627176587658</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>541</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>541.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>15.72</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>15.86</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.73</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.73</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>623.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1134.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1134</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1082.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1477.34</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1477.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-141.4265438596547</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>623</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>623.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>15.81</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>15.73</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.73</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1673.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1135.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1135.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1097.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1483.74</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1483.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-104.1096332945083</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1673</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1673.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>15.9</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>15.92</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.74</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.74</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>882.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1014.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1014.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1244.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1457.48</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1457.48</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-159.5815598694953</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>882</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>882.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>87.16</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>89.38</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>88.4</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>196003.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>79235.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>79235.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>84864.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>113080.18</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>113080.18</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>969.8603274618799</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>196003</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>196003.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>85.64</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>89.34</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>89.34</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>88.34999999999999</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>60783.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>53210.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>53210</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>70175.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>112223.88</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>112223.88</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-10030.79569813701</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>60783</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>60783.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>85.3</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>89.38</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>88.46</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>88.45999999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>24177.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>57766.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>57766.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>69287.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>116801.5</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>116801.5</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-10899.91874548767</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>24177</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>24177.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>85.85999999999999</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>89.57</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>88.55</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>88.55</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>72685.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>61052.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>61052.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>75834.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>119132.7</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>119132.7</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-7830.168857935467</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>72685</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>72685.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>86.55999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>89.62</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>88.71</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>89.62</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>88.70999999999999</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>42528.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>75082.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>75082.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>89412.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>120987.62</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>120987.62</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-8362.448702220325</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>42528</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>42528.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>87.44</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>89.54</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>88.74</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>88.73999999999999</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>65877.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>90493.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>90493.60000000001</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>107436.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>121235.66</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>121235.66</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-5593.082454690855</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>65877</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>65877.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>88.36</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>89.66</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>88.81</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>88.81</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>83565.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>87141.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>87141.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>110364.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>122389.8</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>122389.8</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-3938.770584838363</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>83565</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>83565.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>89.2</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>89.66</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>88.88</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>88.88</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>40609.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>80809.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>80809.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>109441.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>122815.98</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>122815.98</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3329.940392733435</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>40609</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>40609.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>89.92</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>89.58</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>88.93</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>88.93000000000001</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>142835.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>90616.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>90616.39999999999</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>112118.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>125535.6</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>125535.6</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>2261.17203858553</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>142835</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>142835.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>88.99</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>88.98999999999999</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>119582.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>103742.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>103742.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>105992.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>125523.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>125523.74</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-785.0663466225815</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>119582</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>119582.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>91.32000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>89.25</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>88.97</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>88.97</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>49115.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>124380.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>124380.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>110324.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>127685.92</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>127685.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-2617.404527397666</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>49115</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>49115.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>20.29</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>18.56</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>18.56</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>49315.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>62823.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>62823.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>45447.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>35116.58</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>35116.58</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>4898.906430943498</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>49315</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>49315.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>20.07</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>18.5</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>69982.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>57043.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>57043.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>42317.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>34420.9</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>34420.9</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>6052.343923426641</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>69982</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>69982.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>18.44</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>123318.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>46126.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>46126.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>38451.0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>33402.44</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>33402.44</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>5269.635201137324</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>123318</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>123318.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>19.73</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>18.39</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>50773.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>27452.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>27452.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>33200.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>32074.88</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>32074.88</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1751.292802173746</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>50773</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>50773.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>19.72</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>18.33</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>18.33</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>20731.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>27352.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>27352.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>31525.1</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>31314.62</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>31314.62</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-3945.965206826208</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>20731</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>20731.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>19.72</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>19.53</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>18.28</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>20412.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>28071.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>28071.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>33398.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>31047.28</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>31047.28</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-3721.498456085934</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>20412</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>20412.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>19.74</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>19.54</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>18.23</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>18.23</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>15397.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>27592.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>27592</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>33580.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>30760.38</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>30760.38</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-3233.742438739624</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>15397</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>15397.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>19.53</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>18.17</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>18.17</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>29949.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>30775.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>30775.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>35756.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>30595.22</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>30595.22</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-1884.135898289904</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>29949</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>29949.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>19.36</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>18.1</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>50273.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>38947.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>38947.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>37451.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>30086.84</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>30086.84</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-1447.978844137098</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>50273</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>50273.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>19.14</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>18.02</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>18.02</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>24327.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>35697.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>35697.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>35200.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>29195.96</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>29195.96</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-2950.755236628182</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>24327</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>24327.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>19.28</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>19.21</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17.96</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>17.96</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>18014.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>38725.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>38725.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>38182.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>28857.98</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>28857.98</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-2212.265967450156</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>18014</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>18014.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>49.16</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>47.79</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>48.09</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>48.09</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>58151.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>33826.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>33826</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>31804.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>30566.2</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>30566.2</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>1847.910848564396</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>58151</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>58151.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>47.98</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>48.04</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>38893.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>25373.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>25373.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>41099.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>32485.34</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>32485.34</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-162.6197830090241</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>38893</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>38893.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>47.09</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>47.39</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>48.1</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>31012.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>22443.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>22443.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>45329.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>48091.44</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>48091.44</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-965.6414072921507</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>31012</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>31012.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,21 +21267,17 @@
           <t>46.95</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>47.31</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
+      <c r="AM49" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AO49" t="inlineStr">
         <is>
           <t>48.22</t>
         </is>
       </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>48.22</t>
-        </is>
-      </c>
       <c r="AP49" t="inlineStr">
         <is>
           <t>-2163.74</t>
@@ -21604,20 +21318,16 @@
           <t>18517.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>22345.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>22345</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>43701.5</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>52580.36</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>52580.36</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1233.935106007615</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>18517</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>18517.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>47.69</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>48.29</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>48.29</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>22557.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>22850.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>22850.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>42672.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>52972.04</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>52972.04</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-234.3927075294341</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>22557</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>22557.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>48.33</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>48.3</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>48.3</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>15888.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>29783.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>29783.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>41243.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>53373.12</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>53373.12</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>769.0390298511629</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>15888</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>15888.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>49.49</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>48.37</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>48.37</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>24243.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>56824.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>56824.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>41459.8</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>53916.64</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>53916.64</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>2889.582975043049</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>24243</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>24243.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>50.34</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>48.47</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>48.47</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>30520.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>68215.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>68215.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>40169.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>53954.14</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>53954.14</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>4920.553504779913</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>30520</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>30520.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>50.00000000000001</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>48.51</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>48.51</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>21044.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>65058.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>65058</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>38461.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>54408.58</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>54408.58</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>6973.670207804731</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>21044</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>21044.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>49.08</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>47.17</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>48.52</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>48.52</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>57221.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>62493.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>62493.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>37242.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>55416.48</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>55416.48</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>10672.92013327572</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>57221</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>57221.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>47.87</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>48.56</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>48.56</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>151095.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>52702.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>52702.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>32698.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>57013.98</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>57013.98</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>11700.28002204587</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>151095</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>151095.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>56.42</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>56.42</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>24547.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>18738.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>18738.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>18368.7</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>39281.12</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>39281.12</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-4635.859488961043</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>24547</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>24547.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>50.37</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>54.31</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>56.57</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>18715.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>17048.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>17048.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>21040.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>39970.92</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>39970.92</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-5394.524359295392</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>18715</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>18715.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>50.77</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>54.61</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>56.8</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>8783.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>16315.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>16315.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>42883.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>40583.16</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>40583.16</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-5660.812589798199</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>8783</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>8783.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>51.63000000000001</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>55.05</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>57.06</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>57.06</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>26134.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>17830.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>17830.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>45449.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>41499.18</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>41499.18</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-4774.909612309413</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>26134</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>26134.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>52.98</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>55.52</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>57.31</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>15514.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>15750.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>15750</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>43830.8</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>41402.62</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>41402.62</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-5197.837158314382</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>15514</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>15514.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>53.96</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>55.89</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>57.48</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>57.48</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>16098.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>17998.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>17998.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>43270.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>41456.5</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>41456.5</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-4478.525182667399</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>16098</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>16098.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>55.18000000000001</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>56.35</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>57.66</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>57.66</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>15050.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>25032.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>25032.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>43063.9</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>41902.86</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>41902.86</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-3353.560746647869</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>15050</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>15050.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>56.44</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>56.51</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>57.84</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>57.84</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>16356.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>69452.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>69452</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>45821.6</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>42405.08</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>42405.08</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-1514.412954239691</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>16356</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>16356.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>57.99</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>57.99</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>15732.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>73068.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>73068.60000000001</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>47322.7</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>43605.9</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>43605.9</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>1027.098640423406</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>15732</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>15732.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>56.91999999999999</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>56.72</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>58.16</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>58.16</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>26758.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>71911.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>71911.60000000001</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>46992.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>44280.82</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>44280.82</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>4688.004538498419</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>26758</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>26758.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>56.34</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>56.72</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>58.37</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>58.37</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>51265.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>68541.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>68541.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>46257.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>44937.86</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>44937.86</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>8569.084230802073</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>51265</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>51265.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>197.9</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>197.65</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>185.71</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>197.65</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>185.71</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1472045210.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1939773829.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1939773829.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>3455631190.8</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1641863678.44</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1641863678.44</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-185240308.8270531</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1472045210</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1472045210.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>200.5</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>196.2</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>185.54</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>196.2</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>185.54</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1612049356.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>2225091407.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>2225091407.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>3847681976.3</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1618922459.02</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1618922459.02</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-86152374.03783798</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1612049356</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1612049356.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>204.0</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>194.42</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>185.45</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>194.42</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>185.45</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>2227499399.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>3369535826.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>3369535826.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>3905782098.4</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1595265571.84</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1595265571.84</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>43478244.80524874</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>2227499399</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>2227499399.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>209.7</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>192.7</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>185.49</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>192.7</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>185.49</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1805219432.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>4044358245.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>4044358245.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>3848964319.1</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1597584072.62</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1597584072.62</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>161170972.659471</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1805219432</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1805219432.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>212.7</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>191.08</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>185.55</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>191.08</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>185.55</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>2582055752.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4232008889.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4232008889</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>4006630702.4</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1581993912.94</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1581993912.94</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>368791617.0348077</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>2582055752</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>2582055752.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>212.5</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>188.52</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>185.16</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>188.52</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>185.16</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>2898633097.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4971488551.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4971488551.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>4106637961.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1568361256.88</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1568361256.88</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>568988945.5340452</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>2898633097</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>2898633097.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>212.8</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>186.25</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>184.73</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>184.73</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>7334271454.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>5470272545.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>5470272545.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>4567974637.4</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1570183316.24</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1570183316.24</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>800745094.0853124</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>7334271454</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>7334271454.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>208.8</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>183.55</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>184.34</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>183.55</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>184.34</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>5601611492.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>4442028370.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>4442028370</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>4317738015.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1457742036.26</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1457742036.26</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>627980300.4055042</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>5601611492</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>5601611492.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>202.4</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>180.48</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>183.65</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>180.48</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>183.65</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>2743472650.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>3653570392.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>3653570392.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3918089646.3</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>1384527965.68</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>1384527965.68</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>544387723.2055812</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>2743472650</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>2743472650.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>178.82</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>183.55</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>178.82</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>183.55</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>6279454066.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>3781252515.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>3781252515.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3696644209.8</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1369708722.5</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1369708722.5</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>711756498.7340636</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>6279454066</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>6279454066.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>199.1</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>176.95</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>183.61</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>176.95</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>183.61</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>5392553065.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>3241787371.0</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>3241787371</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>3107402238.1</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1301417536.02</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1301417536.02</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>546579722.8199644</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>5392553065</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>5392553065.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>10702402903</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>9579043601</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>16911194399</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>15812987742</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>15882778006</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>10973548400</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>12353712685</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>10709769939</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>18182742782</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>10733728288</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>13958553198</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>39.13</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>40.28</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>5252.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>4706.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>4706</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>5486.1</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>13976.5</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>13976.5</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-1337.93216023667</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>5252</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>5252.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>38.71</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>40.32</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>41.23</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>41.23</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>4244.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>4511.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>4511</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>5797.7</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>14034.58</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>14034.58</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-1435.827728410939</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>4244</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>4244.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>38.62</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>40.37</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>41.26</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>41.26</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>1968.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>4865.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>4865.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>10981.6</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>14030.28</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>14030.28</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-1416.398978359505</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1968</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1968.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>38.93</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>41.31</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>41.31</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>7631.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>5690.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>5690</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>12924.1</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>14047.38</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>14047.38</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-1094.200800487474</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>7631</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>7631.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>39.42</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>40.72</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>4435.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>5640.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>5640</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>12750.4</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>13965.76</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>13965.76</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-1201.589089224306</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>4435</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>4435.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>39.93</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>40.86</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>41.43</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>41.43</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>4277.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>6266.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>6266.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>12638.5</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>13968.3</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>13968.3</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-969.6584628046257</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>4277</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>4277.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>40.73999999999999</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>41.49</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>41.49</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>6015.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>7084.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>7084.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>12478.0</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>13950.6</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>13950.6</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-586.7697656763448</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>6015</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>6015.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>41.71</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>41.55</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>41.55</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>6092.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>17098.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>17098</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>12157.4</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>13875.9</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>13875.9</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-205.0441352903617</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>6092</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>6092.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>42.53</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>41.58</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>41.58</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>7381.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>20158.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>20158.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>11928.2</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>13878.46</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>13878.46</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>339.3511986642698</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>7381</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>7381.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>42.43</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>41.59</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>41.63</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>41.63</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>7566.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>19860.8</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>19860.8</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>11387.1</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>13858.62</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>13858.62</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>966.8319900757324</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>7566</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>7566.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>42.11</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>41.67</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>41.69</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>41.69</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>8368.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>19010.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>19010.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>11009.7</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>13843.62</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>13843.62</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>1808.881978160831</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>8368</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>8368.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>136.4</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>135.85</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>136.76</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>135.85</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>136.76</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>4119.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>2735.2</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>2735.2</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>5560.0</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>5190.6</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>5190.6</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-702.2417591933672</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>4119</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>4119.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>136.0</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>135.7</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>136.8</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>136.8</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>1023.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>2362.8</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>2362.8</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>5383.4</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>5228.58</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>5228.58</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-847.5039936199087</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>1023</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>1023.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>136.1</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>135.62</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>136.87</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>135.62</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>136.87</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>1042.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>2649.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>2649.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>5795.5</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>5259.92</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>5259.92</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-693.0391858856847</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>1042</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>1042.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>136.5</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>135.65</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>136.96</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>135.65</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>136.96</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>3466.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>2971.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>2971</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>5992.6</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>5305.78</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>5305.78</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-449.6594896265906</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>3466</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>3466.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>137.2</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>135.72</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>137.07</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>135.72</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>137.07</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>4026.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>4919.2</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>4919.2</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>6033.4</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>5312.2</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>5312.2</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-345.6292274840762</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>4026</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>4026.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>137.6</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>135.78</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>137.17</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>135.78</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>137.17</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>2257.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>8384.8</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>8384.799999999999</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>5899.5</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>5345.52</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>5345.52</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-244.6706662989109</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>2257</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>2257.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>137.7</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>135.88</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>137.28</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>135.88</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>137.28</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>2455.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>8404.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>8404</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>6746.0</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>5360.06</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>5360.06</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>97.82980204771411</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>2455</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>2455.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>137.2</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>135.85</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>137.35</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>135.85</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>137.35</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>2651.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>8941.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>8941.799999999999</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>7009.1</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>5407.2</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>5407.2</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>562.4079781840455</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>2651</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>2651.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>136.6</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>135.85</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>137.42</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>135.85</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>137.42</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>13207.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>9014.2</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>9014.200000000001</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>7096.1</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>5947.52</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>5947.52</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>1185.005087729376</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>13207</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>13207.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>135.8</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>135.72</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>137.45</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>135.72</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>137.45</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>21354.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>7147.6</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>7147.6</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>6086.9</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>5953.52</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>5953.52</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>901.1079196609408</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>21354</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>21354.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>135.0</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>135.65</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>137.44</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>135.65</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>137.44</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>2353.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>3414.2</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>3414.2</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>4564.1</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>5607.86</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>5607.86</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-409.5347461390011</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>2353</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>2353.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>98.11999999999999</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>95.74</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>92.75</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>92.75</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>17465827.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>9367492.0</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>9367492</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>12240908.6</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>9547426.36</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>9547426.359999999</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-326158.3432660736</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>17465827</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>17465827.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>95.32</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>92.63</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>95.31999999999999</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>92.63</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>4767854.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>6396828.2</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>6396828.2</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>13157633.9</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>9422199.2</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>9422199.199999999</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-1040222.663576726</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>4767854</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>4767854.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>94.96</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>92.58</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>92.58</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>4911165.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>10719716.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>10719716</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>13958338.6</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>9431646.58</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>9431646.58</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-662666.6331784893</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>4911165</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>4911165.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>97.62</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>94.65</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>92.52</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>92.52</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>3178824.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>10818731.2</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>10818731.2</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>15737578.1</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>9398530.84</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>9398530.84</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-114988.9599960633</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>3178824</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>3178824.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>97.72</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>94.35</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>92.46</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>92.45999999999999</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>16513790.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>15976158.6</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>15976158.6</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>17604730.1</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>9405507.58</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>9405507.58</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>857122.4288358316</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>16513790</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>16513790.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>97.28</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>93.94</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>92.38</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>92.38</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>2612508.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>15114325.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>15114325.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>16508494.6</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>9131262.26</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>9131262.26</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>786495.1118515488</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>2612508</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>2612508.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>97.56</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>93.62</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>92.32</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>92.31999999999999</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>26382293.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>19918439.6</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>19918439.6</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>16478862.3</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>9118251.56</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>9118251.560000001</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>2146932.905022157</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>26382293</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>26382293.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>97.36</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>93.34</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>92.26</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>92.26000000000001</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>5406241.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>17196961.2</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>17196961.2</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>14023526.1</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>8669218.56</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>8669218.560000001</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>1466976.612943662</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>5406241</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>5406241.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>97.26</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>92.2</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>28965961.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>20656425.0</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>20656425</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>13799206.0</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>8799268.96</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>8799268.960000001</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>2690652.602369256</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>28965961</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>28965961.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>96.53999999999999</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>92.76</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>92.15</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>92.15000000000001</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>12204623.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>19233301.6</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>19233301.6</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>12350224.7</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>8337280.94</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>8337280.94</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>1818410.708606917</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>12204623</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>12204623.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>95.7</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>92.41</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>92.14</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>92.14</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>26633080.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>17902664.0</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>17902664</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>11808340.8</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>8219127.92</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>8219127.92</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>2303265.263639044</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>26633080</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>26633080.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>14.67</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>15.09</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>65425783.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>52475012.8</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>52475012.8</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>86185131.5</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>39906171.64</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>39906171.64</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>4827100.927857764</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>65425783</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>65425783.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>14.49</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>15.11</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>109784456.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>48976089.4</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>48976089.4</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>82831594.4</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>40943697.7</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>40943697.7</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>5772376.479114637</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>109784456</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>109784456.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>14.32</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>15.14</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>15.14</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>29265572.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>45130268.6</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>45130268.6</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>73682184.3</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>41815330.2</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>41815330.2</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>2163898.856656082</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>29265572</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>29265572.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>14.41</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>28096102.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>105137643.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>105137643.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>72957008.0</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>43530297.42</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>43530297.42</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>5558672.008263297</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>28096102</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>28096102.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>14.84</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>15.28</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>15.28</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>29803151.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>118716855.4</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>118716855.4</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>71217190.0</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>44114417.38</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>44114417.38</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>10335124.29597849</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>29803151</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>29803151.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>14.91</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>15.33</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>15.33</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>47931166.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>119895250.2</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>119895250.2</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>69602925.0</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>44342836.04</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>44342836.04</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>16606617.87500094</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>47931166</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>47931166.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>15.39</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>90555352.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>116687099.4</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>116687099.4</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>66357157.4</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>44770089.04</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>44770089.04</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>23030513.59949727</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>90555352</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>90555352.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>14.87</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>15.44</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>15.44</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>329302448.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>102234100.0</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>102234100</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>59175816.6</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>43949812.2</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>43949812.2</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>26818112.07736713</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>329302448</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>329302448.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>14.76</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>15.49</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>95992160.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>40776372.2</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>40776372.2</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>27593237.5</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>39019565.4</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>39019565.4</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>5691131.328703824</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>95992160</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>95992160.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>14.32</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>15.52</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>35695125.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>23717524.6</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>23717524.6</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>19525180.5</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>38842421.82</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>38842421.82</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>304006.4260168225</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>35695125</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>35695125.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>14.21</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>15.59</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>31890412.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>19310599.8</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>19310599.8</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>18235308.4</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>41063861.78</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>41063861.78</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-942347.0573223457</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>31890412</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>31890412.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
